--- a/Figure S3/Figure S3-A.xlsx
+++ b/Figure S3/Figure S3-A.xlsx
@@ -1,97 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\附图3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure S2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0AC467-0D7F-4085-B1CA-15442CFB2D32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B776C637-9B84-4FE2-ADD2-E3AD6E9BA4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24130" yWindow="1640" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="5" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>CON 1</t>
-  </si>
-  <si>
-    <t>CON 2</t>
-  </si>
-  <si>
-    <t>CON 3</t>
-  </si>
-  <si>
-    <t>CON 4</t>
-  </si>
-  <si>
-    <t>ETEC 1</t>
-  </si>
-  <si>
-    <t>ETEC 2</t>
-  </si>
-  <si>
-    <t>ETEC 3</t>
-  </si>
-  <si>
-    <t>ETEC 4</t>
-  </si>
-  <si>
-    <t>EWK 1</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>ETEC</t>
+  </si>
+  <si>
+    <t>ETEC_WB800</t>
+  </si>
+  <si>
+    <t>ETEC_WB800_KR32</t>
+  </si>
+  <si>
+    <t>Benzenoids</t>
+  </si>
+  <si>
+    <t>Polyketides</t>
+  </si>
+  <si>
+    <t>Nucleic acids</t>
+  </si>
+  <si>
+    <t>Fatty Acyls</t>
+  </si>
+  <si>
+    <t>Organic acids</t>
+  </si>
+  <si>
+    <t>Organoheterocyclic compounds</t>
+  </si>
+  <si>
+    <t>Group</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EWK 2</t>
-  </si>
-  <si>
-    <t>EWK 3</t>
-  </si>
-  <si>
-    <t>EWK 4</t>
-  </si>
-  <si>
-    <t>let-7f-5p</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ETEC 5</t>
-  </si>
-  <si>
-    <t>ETEC 6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -111,14 +107,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -135,7 +144,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -177,12 +186,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -212,12 +221,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -387,134 +396,219 @@
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.1796875" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="11.54296875" style="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
-        <v>12</v>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="B2" s="1">
-        <v>1.89</v>
+        <v>9.6381570371428555</v>
+      </c>
+      <c r="C2" s="1">
+        <v>6.8473171485714284</v>
+      </c>
+      <c r="D2" s="1">
+        <v>7.6797069021428577</v>
+      </c>
+      <c r="E2" s="1">
+        <v>5.6794286736495927</v>
+      </c>
+      <c r="G2" s="2">
+        <v>2.9913661356803574E-2</v>
+      </c>
+      <c r="H2" s="2">
+        <v>2.7577021904705491E-2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>3.4751088850100205E-2</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1.6300121178297801E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B3" s="1">
-        <v>1.24</v>
+        <v>2.5796716601428571</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1.9749655318571426</v>
+      </c>
+      <c r="D3" s="1">
+        <v>4.1677867690000001</v>
+      </c>
+      <c r="E3" s="1">
+        <v>2.3269767417306015</v>
+      </c>
+      <c r="G3" s="2">
+        <v>8.0064502119932563E-3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>7.9540156460294279E-3</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1.8859460414742901E-2</v>
+      </c>
+      <c r="J3" s="2">
+        <v>6.6784891665723871E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="B4" s="1">
-        <v>4.07</v>
+        <v>0.8514558571428571</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.71072385057142851</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0.61461910714285717</v>
+      </c>
+      <c r="E4" s="1">
+        <v>1.0751642915037034</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2.6426382214652885E-3</v>
+      </c>
+      <c r="H4" s="2">
+        <v>2.8623834372114684E-3</v>
+      </c>
+      <c r="I4" s="2">
+        <v>2.7811846823647662E-3</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3.0857519735039349E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B5" s="1">
-        <v>1.51</v>
+        <v>281.9958660685715</v>
+      </c>
+      <c r="C5" s="1">
+        <v>222.82170324571427</v>
+      </c>
+      <c r="D5" s="1">
+        <v>193.31451962428574</v>
+      </c>
+      <c r="E5" s="1">
+        <v>322.0825834212834</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.87522218294281084</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.89739657999233235</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.87475865069844128</v>
+      </c>
+      <c r="J5" s="2">
+        <v>0.9243861382649422</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="B6" s="1">
-        <v>0.25</v>
+        <v>21.247020839285714</v>
+      </c>
+      <c r="C6" s="1">
+        <v>11.014519451285715</v>
+      </c>
+      <c r="D6" s="1">
+        <v>11.482487129142859</v>
+      </c>
+      <c r="E6" s="1">
+        <v>12.551723497365938</v>
+      </c>
+      <c r="G6" s="2">
+        <v>6.5943746691198568E-2</v>
+      </c>
+      <c r="H6" s="2">
+        <v>4.436009572614618E-2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>5.1958874932275738E-2</v>
+      </c>
+      <c r="J6" s="2">
+        <v>3.6023801998393695E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="B7" s="1">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="1">
-        <v>0.14000000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="1">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="1">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0.83</v>
+        <v>5.8870044319999995</v>
+      </c>
+      <c r="C7" s="1">
+        <v>4.9286896782857141</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.7327157247142861</v>
+      </c>
+      <c r="E7" s="1">
+        <v>4.71274004090359</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1.8271320575728403E-2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1.9849903293575062E-2</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1.6890740422074946E-2</v>
+      </c>
+      <c r="J7" s="2">
+        <v>1.3525697418290027E-2</v>
       </c>
     </row>
   </sheetData>
